--- a/output/graficos_dimensiones/comunal_d_env_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:14</t>
+    <t xml:space="preserve">2026-09-10 01:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:28</t>
+    <t xml:space="preserve">2026-09-12 22:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_biobio.xlsx
@@ -69,27 +69,27 @@
     <t xml:space="preserve">Santa Juana</t>
   </si>
   <si>
+    <t xml:space="preserve">Contulmo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laja</t>
+  </si>
+  <si>
     <t xml:space="preserve">Talcahuano</t>
   </si>
   <si>
-    <t xml:space="preserve">Contulmo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laja</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hualpén</t>
   </si>
   <si>
     <t xml:space="preserve">Mulchén</t>
   </si>
   <si>
+    <t xml:space="preserve">Santa Bárbara</t>
+  </si>
+  <si>
     <t xml:space="preserve">Penco</t>
   </si>
   <si>
-    <t xml:space="preserve">Santa Bárbara</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chiguayante</t>
   </si>
   <si>
@@ -105,12 +105,12 @@
     <t xml:space="preserve">Cabrero</t>
   </si>
   <si>
+    <t xml:space="preserve">Lebu</t>
+  </si>
+  <si>
     <t xml:space="preserve">Arauco</t>
   </si>
   <si>
-    <t xml:space="preserve">Lebu</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hualqui</t>
   </si>
   <si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:40</t>
+    <t xml:space="preserve">2026-09-24 00:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -577,7 +577,7 @@
         <v>2018</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>152.01</v>
+        <v>161.98</v>
       </c>
     </row>
     <row r="3">
@@ -594,7 +594,7 @@
         <v>2018</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>127.39</v>
+        <v>137.73</v>
       </c>
     </row>
     <row r="4">
@@ -611,7 +611,7 @@
         <v>2018</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>126.98</v>
+        <v>135.84</v>
       </c>
     </row>
     <row r="5">
@@ -628,7 +628,7 @@
         <v>2018</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>121.53</v>
+        <v>130.98</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         <v>2018</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>119.83</v>
+        <v>126.87</v>
       </c>
     </row>
     <row r="7">
@@ -662,7 +662,7 @@
         <v>2018</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>113.45</v>
+        <v>121.71</v>
       </c>
     </row>
     <row r="8">
@@ -679,7 +679,7 @@
         <v>2018</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>112.86</v>
+        <v>121.27</v>
       </c>
     </row>
     <row r="9">
@@ -696,7 +696,7 @@
         <v>2018</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>108.03</v>
+        <v>116.09</v>
       </c>
     </row>
     <row r="10">
@@ -713,7 +713,7 @@
         <v>2018</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>105.5</v>
+        <v>113.94</v>
       </c>
     </row>
     <row r="11">
@@ -730,7 +730,7 @@
         <v>2018</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>103.69</v>
+        <v>112.11</v>
       </c>
     </row>
     <row r="12">
@@ -747,7 +747,7 @@
         <v>2018</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>99.73</v>
+        <v>107.24</v>
       </c>
     </row>
     <row r="13">
@@ -758,13 +758,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>8110</v>
+        <v>8204</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>98.22</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="14">
@@ -775,13 +775,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>8204</v>
+        <v>8304</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>98.1</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="15">
@@ -792,13 +792,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>8304</v>
+        <v>8110</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>97.57</v>
+        <v>105.47</v>
       </c>
     </row>
     <row r="16">
@@ -815,7 +815,7 @@
         <v>2018</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>96.7</v>
+        <v>103.69</v>
       </c>
     </row>
     <row r="17">
@@ -832,7 +832,7 @@
         <v>2018</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>96.21</v>
+        <v>103.69</v>
       </c>
     </row>
     <row r="18">
@@ -843,13 +843,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>8107</v>
+        <v>8311</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>93.12</v>
+        <v>99.59</v>
       </c>
     </row>
     <row r="19">
@@ -860,13 +860,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>8311</v>
+        <v>8107</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>92.74</v>
+        <v>99.56</v>
       </c>
     </row>
     <row r="20">
@@ -883,7 +883,7 @@
         <v>2018</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>92.2</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="21">
@@ -900,7 +900,7 @@
         <v>2018</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>89.35</v>
+        <v>95.17</v>
       </c>
     </row>
     <row r="22">
@@ -917,7 +917,7 @@
         <v>2018</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>87.34</v>
+        <v>94.94</v>
       </c>
     </row>
     <row r="23">
@@ -934,7 +934,7 @@
         <v>2018</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>86.23</v>
+        <v>93.09</v>
       </c>
     </row>
     <row r="24">
@@ -951,7 +951,7 @@
         <v>2018</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>85.67</v>
+        <v>92.21</v>
       </c>
     </row>
     <row r="25">
@@ -962,13 +962,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>8202</v>
+        <v>8201</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>77.56</v>
+        <v>83.43</v>
       </c>
     </row>
     <row r="26">
@@ -979,13 +979,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>8201</v>
+        <v>8202</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>77.56</v>
+        <v>83.26</v>
       </c>
     </row>
     <row r="27">
@@ -1002,7 +1002,7 @@
         <v>2018</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>76.01</v>
+        <v>82.14</v>
       </c>
     </row>
     <row r="28">
@@ -1019,7 +1019,7 @@
         <v>2018</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>74.23</v>
+        <v>79.66</v>
       </c>
     </row>
     <row r="29">
@@ -1036,7 +1036,7 @@
         <v>2018</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>73.9</v>
+        <v>79.66</v>
       </c>
     </row>
     <row r="30">
@@ -1053,7 +1053,7 @@
         <v>2018</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>71.23</v>
+        <v>77.08</v>
       </c>
     </row>
     <row r="31">
@@ -1070,7 +1070,7 @@
         <v>2018</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>65.75</v>
+        <v>70.64</v>
       </c>
     </row>
     <row r="32">
@@ -1087,7 +1087,7 @@
         <v>2018</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>60.13</v>
+        <v>64.53</v>
       </c>
     </row>
     <row r="33">
@@ -1104,7 +1104,7 @@
         <v>2018</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>57.61</v>
+        <v>61.81</v>
       </c>
     </row>
     <row r="34">
@@ -1121,7 +1121,7 @@
         <v>2018</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>39.95</v>
+        <v>42.84</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:08</t>
+    <t xml:space="preserve">2026-10-02 15:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_biobio.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Hualqui</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Coronel</t>
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Cañete</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">San Pedro de la Paz</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:40</t>
+    <t xml:space="preserve">2026-10-04 10:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:37</t>
+    <t xml:space="preserve">2026-10-05 16:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
